--- a/NBFC-MF/Borrowers/Sudhana_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Sudhana_Weekly.xlsx
@@ -1557,31 +1557,33 @@
       <c r="K5" s="25"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B6" s="22">
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>318.4654258262637</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="4"/>
+        <v>1081.5345741737362</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="5"/>
+        <v>14800.790431951375</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="2"/>
+        <v>5199.2095680486254</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>13</v>
@@ -1786,7 +1788,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1821,7 +1823,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>18200</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1856,7 +1858,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>15882.325006125111</v>
+        <v>14800.790431951375</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1891,7 +1893,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>4117.674993874889</v>
+        <v>5199.2095680486254</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Sudhana_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Sudhana_Weekly.xlsx
@@ -1591,31 +1591,33 @@
       <c r="K6" s="25"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A7" s="19">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="23">
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>296.77896817115123</v>
+      </c>
+      <c r="F7" s="21">
+        <f t="shared" si="4"/>
+        <v>1103.2210318288487</v>
+      </c>
+      <c r="G7" s="21">
+        <f t="shared" si="5"/>
+        <v>13697.569400122526</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>6302.4305998774744</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>6</v>
@@ -1788,7 +1790,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1823,7 +1825,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>16800</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1858,7 +1860,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>14800.790431951375</v>
+        <v>13697.569400122526</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1893,7 +1895,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>5199.2095680486254</v>
+        <v>6302.4305998774744</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Sudhana_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Sudhana_Weekly.xlsx
@@ -1627,31 +1627,33 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A8" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B8" s="22">
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H8" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="1"/>
+        <v>274.657663164084</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="4"/>
+        <v>1125.3423368359161</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="5"/>
+        <v>12572.227063286609</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="2"/>
+        <v>7427.7729367133907</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>14</v>
@@ -1662,31 +1664,33 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A9" s="19">
+        <v>46305</v>
+      </c>
+      <c r="B9" s="23">
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>252.09279143638921</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="4"/>
+        <v>1147.9072085636108</v>
+      </c>
+      <c r="G9" s="21">
+        <f t="shared" si="5"/>
+        <v>11424.319854722999</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>8575.6801452770014</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>7</v>
@@ -1790,7 +1794,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1825,7 +1829,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>15400</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1860,7 +1864,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>13697.569400122526</v>
+        <v>11424.319854722999</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1895,7 +1899,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>6302.4305998774744</v>
+        <v>8575.6801452770014</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
